--- a/data/trans_orig/P70D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de su capacidad laboral actual en 2023</t>
+          <t>Población según su autopercepción de su capacidad laboral actual en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -728,12 +728,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46734</t>
+          <t>48094</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>32653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47734</t>
+          <t>46688</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74634</t>
+          <t>72474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38160</t>
+          <t>39693</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28341</t>
+          <t>29648</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54825</t>
+          <t>55228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36308</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60046</t>
+          <t>60753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53621</t>
+          <t>53529</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81818</t>
+          <t>83008</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25218</t>
+          <t>24750</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23899</t>
+          <t>22799</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>31591</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1616,97 +1616,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1766</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3569</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>631</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3488</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2978</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3408</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1873,62 +1873,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4538</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>889</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>240020</t>
+          <t>229505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>522925</t>
+          <t>528947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>232644</t>
+          <t>228310</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>352930</t>
+          <t>364577</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>489839</t>
+          <t>480167</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>826767</t>
+          <t>820621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368250</t>
+          <t>366208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>917167</t>
+          <t>913516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211062</t>
+          <t>209532</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>429478</t>
+          <t>428943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>610452</t>
+          <t>621621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1300420</t>
+          <t>1326797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>160756</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>352789</t>
+          <t>351060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>200157</t>
+          <t>200899</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>299505</t>
+          <t>299718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385414</t>
+          <t>381207</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>635028</t>
+          <t>630079</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41114</t>
+          <t>42425</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99545</t>
+          <t>103109</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54407</t>
+          <t>54150</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89781</t>
+          <t>92608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101738</t>
+          <t>100487</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179200</t>
+          <t>177599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43548</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30587</t>
+          <t>30080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33964</t>
+          <t>33891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66758</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29972</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2732,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3004,42 +3004,42 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>3810</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>8254</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3810</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>8082</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>789</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>135133</t>
+          <t>134005</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>182093</t>
+          <t>179665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>130547</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>164960</t>
+          <t>166318</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>279497</t>
+          <t>279474</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>338017</t>
+          <t>339571</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>104731</t>
+          <t>105239</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>145736</t>
+          <t>146080</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>110850</t>
+          <t>109726</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143272</t>
+          <t>142437</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>226729</t>
+          <t>224032</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>280560</t>
+          <t>276272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104995</t>
+          <t>104864</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>144629</t>
+          <t>145492</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>105272</t>
+          <t>107147</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>139869</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>220263</t>
+          <t>221330</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>273796</t>
+          <t>273093</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39770</t>
+          <t>39578</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28640</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>32521</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>61496</t>
+          <t>61931</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24277</t>
+          <t>23866</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34835</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19945</t>
+          <t>19308</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>411</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>835</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>535</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>522</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4292,97 +4292,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>601</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -4403,97 +4403,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>1569</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4514,97 +4514,97 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>1569</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>423283</t>
+          <t>368363</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>719483</t>
+          <t>719258</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>398745</t>
+          <t>401327</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>529166</t>
+          <t>527979</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>786497</t>
+          <t>845050</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1194246</t>
+          <t>1196133</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>514916</t>
+          <t>510601</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1118196</t>
+          <t>1212007</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>354699</t>
+          <t>355541</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>590841</t>
+          <t>580236</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>903833</t>
+          <t>899472</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1738254</t>
+          <t>1675408</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>304009</t>
+          <t>265230</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>531515</t>
+          <t>533333</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>341347</t>
+          <t>346318</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>446170</t>
+          <t>444697</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>664300</t>
+          <t>688802</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>955190</t>
+          <t>954870</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>68514</t>
+          <t>70866</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>139766</t>
+          <t>140331</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>80533</t>
+          <t>79725</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>117241</t>
+          <t>116019</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>162426</t>
+          <t>166940</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>245670</t>
+          <t>245079</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>32370</t>
+          <t>31019</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>66674</t>
+          <t>65903</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>26509</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>47764</t>
+          <t>48159</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>63178</t>
+          <t>63809</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>105417</t>
+          <t>104644</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>22223</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>49979</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>29033</t>
+          <t>28479</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>61460</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -5408,12 +5408,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5534,82 +5534,82 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>5672</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>11129</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>9163</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>4762</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>5672</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>2453</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>10777</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>9163</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>5096</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>16522</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -5741,12 +5741,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>12844</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Estudios-trans_orig.xlsx
@@ -723,32 +723,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35747</t>
+          <t>50386</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25867</t>
+          <t>38448</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48094</t>
+          <t>66431</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -758,32 +758,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23941</t>
+          <t>27262</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32653</t>
+          <t>36014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59688</t>
+          <t>77648</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46688</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72474</t>
+          <t>95284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -834,32 +834,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24768</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16478</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39693</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>48388</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55228</t>
+          <t>62459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -945,32 +945,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48082</t>
+          <t>52839</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>40479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60753</t>
+          <t>67081</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -980,32 +980,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1015,32 +1015,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>67440</t>
+          <t>75927</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53529</t>
+          <t>61671</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83008</t>
+          <t>90901</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -1056,67 +1056,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6777</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3359</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10812</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5271</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2471</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9453</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24750</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -1167,32 +1167,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1202,32 +1202,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1237,32 +1237,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1313,32 +1313,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1348,32 +1348,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31591</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>664</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>895</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>569</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>870</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>648</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>903</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>903</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1946,17 +1946,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>130784</t>
+          <t>162433</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130784</t>
+          <t>162433</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130784</t>
+          <t>162433</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>87033</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>87033</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>87033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>210566</t>
+          <t>249466</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>210566</t>
+          <t>249466</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>210566</t>
+          <t>249466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2061,32 +2061,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>421365</t>
+          <t>478255</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229505</t>
+          <t>438031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>528947</t>
+          <t>520416</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>288316</t>
+          <t>289422</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>228310</t>
+          <t>265163</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>364577</t>
+          <t>317692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2131,32 +2131,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>709681</t>
+          <t>767676</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>480167</t>
+          <t>725541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>820621</t>
+          <t>820520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -2172,69 +2172,69 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>556429</t>
+          <t>338048</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>366208</t>
+          <t>303769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>913516</t>
+          <t>379008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>226690</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>204699</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>250607</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>23,97%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>21,64%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>26,5%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>66,12%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>275052</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>209532</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>428943</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>29,09%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>22,16%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>45,37%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>590</t>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>831481</t>
+          <t>564737</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>621621</t>
+          <t>523237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1326797</t>
+          <t>609513</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -2283,32 +2283,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>281399</t>
+          <t>312770</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>160756</t>
+          <t>279548</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>351060</t>
+          <t>348837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2318,32 +2318,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>263092</t>
+          <t>299842</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>200899</t>
+          <t>274887</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>299718</t>
+          <t>328597</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2353,32 +2353,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>544491</t>
+          <t>612612</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>381207</t>
+          <t>563180</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>630079</t>
+          <t>653564</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -2394,32 +2394,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74907</t>
+          <t>92007</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>71460</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103109</t>
+          <t>114452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2429,32 +2429,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72369</t>
+          <t>76377</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54150</t>
+          <t>63107</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92608</t>
+          <t>91071</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2464,32 +2464,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>147276</t>
+          <t>168384</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100487</t>
+          <t>144995</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177599</t>
+          <t>198791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -2505,32 +2505,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>30108</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>44319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2540,32 +2540,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30080</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2575,32 +2575,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>49816</t>
+          <t>55955</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33891</t>
+          <t>42493</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66940</t>
+          <t>71537</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -2616,32 +2616,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2651,32 +2651,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2686,32 +2686,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>22756</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30150</t>
+          <t>34046</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -2727,32 +2727,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2762,32 +2762,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2797,32 +2797,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -2838,32 +2838,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2908,32 +2908,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2984,67 +2984,67 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>3831</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>7882</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3810</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1273</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>8254</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>831</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3171,32 +3171,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3284,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1381684</t>
+          <t>1271300</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1381684</t>
+          <t>1271300</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1381684</t>
+          <t>1271300</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>945405</t>
+          <t>945803</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>945405</t>
+          <t>945803</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>945405</t>
+          <t>945803</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2327089</t>
+          <t>2217103</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2327089</t>
+          <t>2217103</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2327089</t>
+          <t>2217103</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3399,32 +3399,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>158812</t>
+          <t>164243</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>134005</t>
+          <t>141569</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>179665</t>
+          <t>186272</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>148698</t>
+          <t>160292</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>130547</t>
+          <t>143047</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>166318</t>
+          <t>179260</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>307510</t>
+          <t>324535</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>279474</t>
+          <t>291812</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>339571</t>
+          <t>351703</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -3510,32 +3510,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>124969</t>
+          <t>142374</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105239</t>
+          <t>120369</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>146080</t>
+          <t>166445</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>125966</t>
+          <t>138339</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>109726</t>
+          <t>121330</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142437</t>
+          <t>155987</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3580,32 +3580,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>250936</t>
+          <t>280713</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>224032</t>
+          <t>252956</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>276272</t>
+          <t>310088</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -3621,32 +3621,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>124529</t>
+          <t>136505</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104864</t>
+          <t>116338</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>145492</t>
+          <t>160605</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3656,32 +3656,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>122560</t>
+          <t>136633</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107147</t>
+          <t>120042</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>139869</t>
+          <t>154173</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3691,32 +3691,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>247089</t>
+          <t>273138</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>221330</t>
+          <t>245031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>273093</t>
+          <t>301153</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -3732,32 +3732,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24499</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39578</t>
+          <t>47088</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3767,32 +3767,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>23686</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>16339</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29198</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3802,32 +3802,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>44514</t>
+          <t>53494</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32521</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>61931</t>
+          <t>71567</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -3843,32 +3843,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>23866</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3878,32 +3878,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3913,32 +3913,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>22937</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>36432</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -3954,22 +3954,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3989,32 +3989,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4024,32 +4024,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19308</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>811</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4100,22 +4100,22 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>432</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -4211,32 +4211,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4246,22 +4246,22 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>613</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>613</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -4622,17 +4622,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4657,17 +4657,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>438290</t>
+          <t>481306</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>438290</t>
+          <t>481306</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>438290</t>
+          <t>481306</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>888885</t>
+          <t>972953</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>888885</t>
+          <t>972953</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>888885</t>
+          <t>972953</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4737,32 +4737,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>615923</t>
+          <t>692884</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>368363</t>
+          <t>644215</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>719258</t>
+          <t>743253</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4772,17 +4772,17 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>460955</t>
+          <t>476976</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>401327</t>
+          <t>445439</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>527979</t>
+          <t>512441</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4807,32 +4807,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1076879</t>
+          <t>1169859</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>845050</t>
+          <t>1113466</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1196133</t>
+          <t>1231419</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>706166</t>
+          <t>512796</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>510601</t>
+          <t>468226</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1212007</t>
+          <t>560450</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>416076</t>
+          <t>381043</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>355541</t>
+          <t>349982</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>580236</t>
+          <t>413229</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1122243</t>
+          <t>893839</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>899472</t>
+          <t>840422</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1675408</t>
+          <t>949180</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -4959,32 +4959,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>454010</t>
+          <t>502113</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>265230</t>
+          <t>457559</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>533333</t>
+          <t>546303</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4994,32 +4994,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>405010</t>
+          <t>459564</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>346318</t>
+          <t>429205</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>444697</t>
+          <t>492479</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5029,32 +5029,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>859021</t>
+          <t>961677</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>688802</t>
+          <t>905699</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>954870</t>
+          <t>1017124</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -5070,32 +5070,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>110058</t>
+          <t>134548</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>70866</t>
+          <t>111205</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>140331</t>
+          <t>163978</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>97655</t>
+          <t>106840</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>79725</t>
+          <t>90679</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>116019</t>
+          <t>124974</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5140,32 +5140,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>207713</t>
+          <t>241388</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>166940</t>
+          <t>210549</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>245079</t>
+          <t>275383</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -5181,32 +5181,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>31019</t>
+          <t>39347</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>65903</t>
+          <t>70168</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5216,32 +5216,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>35983</t>
+          <t>40854</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>26050</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>53551</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5251,32 +5251,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>84909</t>
+          <t>94702</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>78816</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>104644</t>
+          <t>116245</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5292,32 +5292,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22282</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>49979</t>
+          <t>40416</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5362,32 +5362,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>28479</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>61460</t>
+          <t>54326</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -5403,32 +5403,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5438,32 +5438,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5473,32 +5473,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -5514,102 +5514,102 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>6238</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>12512</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>6165</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>17637</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>5672</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>11129</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>9163</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>4762</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>15102</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -5660,17 +5660,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9757</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5695,17 +5695,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -5736,17 +5736,17 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -5847,32 +5847,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5917,17 +5917,17 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -5960,17 +5960,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1963062</t>
+          <t>1925380</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1963062</t>
+          <t>1925380</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1963062</t>
+          <t>1925380</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5995,17 +5995,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>1463477</t>
+          <t>1514142</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1463477</t>
+          <t>1514142</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1463477</t>
+          <t>1514142</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6030,17 +6030,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>3426540</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>3426540</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3426540</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
